--- a/financials/pnl-sloane-pearl.xlsx
+++ b/financials/pnl-sloane-pearl.xlsx
@@ -6,7 +6,7 @@
   <sheets>
     <sheet sheetId="1" name="Template" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -977,10 +977,10 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20">
-        <v>4384.42</v>
+        <v>4989.47</v>
       </c>
       <c r="E23" s="20">
-        <v>9375.23</v>
+        <v>10674.44</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="21">

--- a/financials/pnl-sloane-pearl.xlsx
+++ b/financials/pnl-sloane-pearl.xlsx
@@ -744,15 +744,15 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20">
-        <v>2076.39</v>
+        <v>1958.76</v>
       </c>
       <c r="E9" s="20">
-        <v>11796.56</v>
+        <v>12020.42</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="21">
-        <f t="shared" ref="G9:G10" si="0">SUM(C9:F9)</f>
-        <v>0</v>
+        <f>SUM(C9:F9)</f>
+        <v>13979.18</v>
       </c>
       <c r="H9" s="18"/>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="21">
-        <f t="shared" si="0"/>
+        <f>SUM(C10:F10)</f>
         <v>0</v>
       </c>
       <c r="H10" s="22"/>
@@ -781,24 +781,24 @@
         <v>15</v>
       </c>
       <c r="C11" s="26">
-        <f t="shared" ref="C11:G11" si="1">SUM(C9:C10)</f>
+        <f>SUM(C9:C10)</f>
         <v>0</v>
       </c>
       <c r="D11" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(D9:D10)</f>
+        <v>1958.76</v>
       </c>
       <c r="E11" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(E9:E10)</f>
+        <v>12020.42</v>
       </c>
       <c r="F11" s="26">
-        <f t="shared" si="1"/>
+        <f>SUM(F9:F10)</f>
         <v>0</v>
       </c>
       <c r="G11" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(G9:G10)</f>
+        <v>13979.18</v>
       </c>
       <c r="H11" s="8"/>
     </row>
@@ -846,7 +846,7 @@
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
       <c r="G15" s="21">
-        <f t="shared" ref="G15:G17" si="2">SUM(C15:F15)</f>
+        <f>SUM(C15:F15)</f>
         <v>0</v>
       </c>
       <c r="H15" s="18"/>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="21">
-        <f t="shared" si="2"/>
+        <f>SUM(C16:F16)</f>
         <v>0</v>
       </c>
       <c r="H16" s="18"/>
@@ -881,15 +881,15 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20">
-        <v>37.72</v>
+        <v>37.65</v>
       </c>
       <c r="E17" s="20">
-        <v>149.7</v>
+        <v>150.61</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>SUM(C17:F17)</f>
+        <v>188.26</v>
       </c>
       <c r="H17" s="18"/>
     </row>
@@ -915,7 +915,7 @@
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
       <c r="G19" s="21">
-        <f t="shared" ref="G19:G21" si="3">SUM(C19:F19)</f>
+        <f>SUM(C19:F19)</f>
         <v>0</v>
       </c>
       <c r="H19" s="18"/>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="21">
-        <f t="shared" si="3"/>
+        <f>SUM(C20:F20)</f>
         <v>0</v>
       </c>
       <c r="H20" s="18"/>
@@ -953,7 +953,7 @@
       <c r="E21" s="20"/>
       <c r="F21" s="20"/>
       <c r="G21" s="21">
-        <f t="shared" si="3"/>
+        <f>SUM(C21:F21)</f>
         <v>0</v>
       </c>
       <c r="H21" s="18"/>
@@ -977,15 +977,15 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20">
-        <v>4989.47</v>
+        <v>5837.7</v>
       </c>
       <c r="E23" s="20">
-        <v>10674.44</v>
+        <v>14070.66</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="21">
         <f>SUM(C23:F23)</f>
-        <v>0</v>
+        <v>19908.36</v>
       </c>
       <c r="H23" s="22"/>
     </row>
@@ -995,24 +995,24 @@
         <v>25</v>
       </c>
       <c r="C24" s="26">
-        <f t="shared" ref="C24:G24" si="4">C15+C16+C17+C19+C20+C21+C23</f>
+        <f>C15+C16+C17+C19+C20+C21+C23</f>
         <v>0</v>
       </c>
       <c r="D24" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>D15+D16+D17+D19+D20+D21+D23</f>
+        <v>5875.35</v>
       </c>
       <c r="E24" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>E15+E16+E17+E19+E20+E21+E23</f>
+        <v>14221.27</v>
       </c>
       <c r="F24" s="26">
-        <f t="shared" si="4"/>
+        <f>F15+F16+F17+F19+F20+F21+F23</f>
         <v>0</v>
       </c>
       <c r="G24" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>G15+G16+G17+G19+G20+G21+G23</f>
+        <v>20096.62</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -1032,24 +1032,24 @@
         <v>26</v>
       </c>
       <c r="C26" s="32">
-        <f t="shared" ref="C26:F26" si="5">C11-C24</f>
+        <f>C11-C24</f>
         <v>0</v>
       </c>
       <c r="D26" s="32">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>D11-D24</f>
+        <v>-3916.59</v>
       </c>
       <c r="E26" s="32">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>E11-E24</f>
+        <v>-2200.85</v>
       </c>
       <c r="F26" s="32">
-        <f t="shared" si="5"/>
+        <f>F11-F24</f>
         <v>0</v>
       </c>
       <c r="G26" s="32">
         <f>SUM(C26:F26)</f>
-        <v>0</v>
+        <v>-6117.44</v>
       </c>
       <c r="H26" s="7"/>
     </row>

--- a/financials/pnl-sloane-pearl.xlsx
+++ b/financials/pnl-sloane-pearl.xlsx
@@ -843,11 +843,13 @@
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+      <c r="E15" s="20">
+        <v>105</v>
+      </c>
       <c r="F15" s="20"/>
       <c r="G15" s="21">
         <f>SUM(C15:F15)</f>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H15" s="18"/>
     </row>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E24" s="26">
         <f>E15+E16+E17+E19+E20+E21+E23</f>
-        <v>14221.27</v>
+        <v>14326.27</v>
       </c>
       <c r="F24" s="26">
         <f>F15+F16+F17+F19+F20+F21+F23</f>
@@ -1012,7 +1014,7 @@
       </c>
       <c r="G24" s="26">
         <f>G15+G16+G17+G19+G20+G21+G23</f>
-        <v>20096.62</v>
+        <v>20201.62</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -1041,7 +1043,7 @@
       </c>
       <c r="E26" s="32">
         <f>E11-E24</f>
-        <v>-2200.85</v>
+        <v>-2305.85</v>
       </c>
       <c r="F26" s="32">
         <f>F11-F24</f>
@@ -1049,7 +1051,7 @@
       </c>
       <c r="G26" s="32">
         <f>SUM(C26:F26)</f>
-        <v>-6117.44</v>
+        <v>-6222.44</v>
       </c>
       <c r="H26" s="7"/>
     </row>

--- a/financials/pnl-sloane-pearl.xlsx
+++ b/financials/pnl-sloane-pearl.xlsx
@@ -747,12 +747,14 @@
         <v>1958.76</v>
       </c>
       <c r="E9" s="20">
-        <v>12020.42</v>
-      </c>
-      <c r="F9" s="20"/>
+        <v>13653.14</v>
+      </c>
+      <c r="F9" s="20">
+        <v>3029.38</v>
+      </c>
       <c r="G9" s="21">
         <f>SUM(C9:F9)</f>
-        <v>13979.18</v>
+        <v>18641.28</v>
       </c>
       <c r="H9" s="18"/>
     </row>
@@ -768,7 +770,9 @@
       <c r="E10" s="24">
         <v>0</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="24">
+        <v>0</v>
+      </c>
       <c r="G10" s="21">
         <f>SUM(C10:F10)</f>
         <v>0</v>
@@ -790,15 +794,15 @@
       </c>
       <c r="E11" s="26">
         <f>SUM(E9:E10)</f>
-        <v>12020.42</v>
+        <v>13653.14</v>
       </c>
       <c r="F11" s="26">
         <f>SUM(F9:F10)</f>
-        <v>0</v>
+        <v>3029.38</v>
       </c>
       <c r="G11" s="26">
         <f>SUM(G9:G10)</f>
-        <v>13979.18</v>
+        <v>18641.28</v>
       </c>
       <c r="H11" s="8"/>
     </row>
@@ -883,15 +887,17 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20">
-        <v>37.65</v>
+        <v>37.77</v>
       </c>
       <c r="E17" s="20">
-        <v>150.61</v>
-      </c>
-      <c r="F17" s="20"/>
+        <v>175.85</v>
+      </c>
+      <c r="F17" s="20">
+        <v>38.95</v>
+      </c>
       <c r="G17" s="21">
         <f>SUM(C17:F17)</f>
-        <v>188.26</v>
+        <v>252.57</v>
       </c>
       <c r="H17" s="18"/>
     </row>
@@ -979,15 +985,17 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20">
-        <v>5837.7</v>
+        <v>6018.16</v>
       </c>
       <c r="E23" s="20">
-        <v>14070.66</v>
-      </c>
-      <c r="F23" s="20"/>
+        <v>17170.15</v>
+      </c>
+      <c r="F23" s="20">
+        <v>4432.49</v>
+      </c>
       <c r="G23" s="21">
         <f>SUM(C23:F23)</f>
-        <v>19908.36</v>
+        <v>27620.8</v>
       </c>
       <c r="H23" s="22"/>
     </row>
@@ -1002,19 +1010,19 @@
       </c>
       <c r="D24" s="26">
         <f>D15+D16+D17+D19+D20+D21+D23</f>
-        <v>5875.35</v>
+        <v>6055.93</v>
       </c>
       <c r="E24" s="26">
         <f>E15+E16+E17+E19+E20+E21+E23</f>
-        <v>14326.27</v>
+        <v>17451</v>
       </c>
       <c r="F24" s="26">
         <f>F15+F16+F17+F19+F20+F21+F23</f>
-        <v>0</v>
+        <v>4471.44</v>
       </c>
       <c r="G24" s="26">
         <f>G15+G16+G17+G19+G20+G21+G23</f>
-        <v>20201.62</v>
+        <v>27978.37</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -1039,19 +1047,19 @@
       </c>
       <c r="D26" s="32">
         <f>D11-D24</f>
-        <v>-3916.59</v>
+        <v>-4097.17</v>
       </c>
       <c r="E26" s="32">
         <f>E11-E24</f>
-        <v>-2305.85</v>
+        <v>-3797.86</v>
       </c>
       <c r="F26" s="32">
         <f>F11-F24</f>
-        <v>0</v>
+        <v>-1442.06</v>
       </c>
       <c r="G26" s="32">
         <f>SUM(C26:F26)</f>
-        <v>-6222.44</v>
+        <v>-9337.09</v>
       </c>
       <c r="H26" s="7"/>
     </row>

--- a/financials/pnl-sloane-pearl.xlsx
+++ b/financials/pnl-sloane-pearl.xlsx
@@ -869,14 +869,14 @@
         <v>0</v>
       </c>
       <c r="E16" s="20">
-        <v>0</v>
+        <v>62.49</v>
       </c>
       <c r="F16" s="20">
         <v>0</v>
       </c>
       <c r="G16" s="21">
         <f>SUM(C16:F16)</f>
-        <v>0</v>
+        <v>62.49</v>
       </c>
       <c r="H16" s="18"/>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E24" s="26">
         <f>E15+E16+E17+E19+E20+E21+E23</f>
-        <v>17451</v>
+        <v>17513.49</v>
       </c>
       <c r="F24" s="26">
         <f>F15+F16+F17+F19+F20+F21+F23</f>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="G24" s="26">
         <f>G15+G16+G17+G19+G20+G21+G23</f>
-        <v>27978.37</v>
+        <v>28040.86</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E26" s="32">
         <f>E11-E24</f>
-        <v>-3797.86</v>
+        <v>-3860.35</v>
       </c>
       <c r="F26" s="32">
         <f>F11-F24</f>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="G26" s="32">
         <f>SUM(C26:F26)</f>
-        <v>-9337.09</v>
+        <v>-9399.58</v>
       </c>
       <c r="H26" s="7"/>
     </row>

--- a/financials/pnl-sloane-pearl.xlsx
+++ b/financials/pnl-sloane-pearl.xlsx
@@ -747,10 +747,10 @@
         <v>1958.76</v>
       </c>
       <c r="E9" s="20">
-        <v>13653.14</v>
+        <v>13377.32</v>
       </c>
       <c r="F9" s="20">
-        <v>3029.38</v>
+        <v>3305.2</v>
       </c>
       <c r="G9" s="21">
         <f>SUM(C9:F9)</f>
@@ -794,11 +794,11 @@
       </c>
       <c r="E11" s="26">
         <f>SUM(E9:E10)</f>
-        <v>13653.14</v>
+        <v>13377.32</v>
       </c>
       <c r="F11" s="26">
         <f>SUM(F9:F10)</f>
-        <v>3029.38</v>
+        <v>3305.2</v>
       </c>
       <c r="G11" s="26">
         <f>SUM(G9:G10)</f>
@@ -985,17 +985,17 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20">
-        <v>6018.16</v>
+        <v>5983.46</v>
       </c>
       <c r="E23" s="20">
-        <v>17170.15</v>
+        <v>17115.91</v>
       </c>
       <c r="F23" s="20">
-        <v>4432.49</v>
+        <v>4451.14</v>
       </c>
       <c r="G23" s="21">
         <f>SUM(C23:F23)</f>
-        <v>27620.8</v>
+        <v>27550.51</v>
       </c>
       <c r="H23" s="22"/>
     </row>
@@ -1010,19 +1010,19 @@
       </c>
       <c r="D24" s="26">
         <f>D15+D16+D17+D19+D20+D21+D23</f>
-        <v>6055.93</v>
+        <v>6021.23</v>
       </c>
       <c r="E24" s="26">
         <f>E15+E16+E17+E19+E20+E21+E23</f>
-        <v>17513.49</v>
+        <v>17459.25</v>
       </c>
       <c r="F24" s="26">
         <f>F15+F16+F17+F19+F20+F21+F23</f>
-        <v>4471.44</v>
+        <v>4490.09</v>
       </c>
       <c r="G24" s="26">
         <f>G15+G16+G17+G19+G20+G21+G23</f>
-        <v>28040.86</v>
+        <v>27970.57</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -1047,19 +1047,19 @@
       </c>
       <c r="D26" s="32">
         <f>D11-D24</f>
-        <v>-4097.17</v>
+        <v>-4062.47</v>
       </c>
       <c r="E26" s="32">
         <f>E11-E24</f>
-        <v>-3860.35</v>
+        <v>-4081.93</v>
       </c>
       <c r="F26" s="32">
         <f>F11-F24</f>
-        <v>-1442.06</v>
+        <v>-1184.89</v>
       </c>
       <c r="G26" s="32">
         <f>SUM(C26:F26)</f>
-        <v>-9399.58</v>
+        <v>-9329.29</v>
       </c>
       <c r="H26" s="7"/>
     </row>

--- a/financials/pnl-sloane-pearl.xlsx
+++ b/financials/pnl-sloane-pearl.xlsx
@@ -887,17 +887,17 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20">
-        <v>37.77</v>
+        <v>37.88</v>
       </c>
       <c r="E17" s="20">
-        <v>175.85</v>
+        <v>172.84</v>
       </c>
       <c r="F17" s="20">
-        <v>38.95</v>
+        <v>42.62</v>
       </c>
       <c r="G17" s="21">
         <f>SUM(C17:F17)</f>
-        <v>252.57</v>
+        <v>253.34</v>
       </c>
       <c r="H17" s="18"/>
     </row>
@@ -1010,19 +1010,19 @@
       </c>
       <c r="D24" s="26">
         <f>D15+D16+D17+D19+D20+D21+D23</f>
-        <v>6021.23</v>
+        <v>6021.34</v>
       </c>
       <c r="E24" s="26">
         <f>E15+E16+E17+E19+E20+E21+E23</f>
-        <v>17459.25</v>
+        <v>17456.24</v>
       </c>
       <c r="F24" s="26">
         <f>F15+F16+F17+F19+F20+F21+F23</f>
-        <v>4490.09</v>
+        <v>4493.76</v>
       </c>
       <c r="G24" s="26">
         <f>G15+G16+G17+G19+G20+G21+G23</f>
-        <v>27970.57</v>
+        <v>27971.34</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -1047,19 +1047,19 @@
       </c>
       <c r="D26" s="32">
         <f>D11-D24</f>
-        <v>-4062.47</v>
+        <v>-4062.58</v>
       </c>
       <c r="E26" s="32">
         <f>E11-E24</f>
-        <v>-4081.93</v>
+        <v>-4078.92</v>
       </c>
       <c r="F26" s="32">
         <f>F11-F24</f>
-        <v>-1184.89</v>
+        <v>-1188.56</v>
       </c>
       <c r="G26" s="32">
         <f>SUM(C26:F26)</f>
-        <v>-9329.29</v>
+        <v>-9330.06</v>
       </c>
       <c r="H26" s="7"/>
     </row>
